--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/36.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/36.xlsx
@@ -426,13 +426,13 @@
         <v>-8.320106430511764</v>
       </c>
       <c r="E2">
-        <v>-5.219475933208379</v>
+        <v>-6.535740302173876</v>
       </c>
       <c r="F2">
-        <v>-0.6198243996574322</v>
+        <v>-1.007590636214506</v>
       </c>
       <c r="G2">
-        <v>-6.113569045312738</v>
+        <v>-5.798335588517797</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.727604964847951</v>
       </c>
       <c r="E3">
-        <v>-6.490152154338658</v>
+        <v>-8.382338790651657</v>
       </c>
       <c r="F3">
-        <v>-0.8799491598519358</v>
+        <v>-1.013673338053263</v>
       </c>
       <c r="G3">
-        <v>-5.34194709101941</v>
+        <v>-5.346777176961207</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.118540470474173</v>
       </c>
       <c r="E4">
-        <v>-7.707288227276251</v>
+        <v>-7.865449710468146</v>
       </c>
       <c r="F4">
-        <v>-0.5356465325523493</v>
+        <v>-1.16383481062834</v>
       </c>
       <c r="G4">
-        <v>-5.189830834035439</v>
+        <v>-5.624955697535087</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.569286137840715</v>
       </c>
       <c r="E5">
-        <v>-7.412366829052711</v>
+        <v>-9.278695878781912</v>
       </c>
       <c r="F5">
-        <v>-0.4698882430159161</v>
+        <v>-1.470622334989943</v>
       </c>
       <c r="G5">
-        <v>-5.211789682597424</v>
+        <v>-4.99959033462122</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.067547439914066</v>
       </c>
       <c r="E6">
-        <v>-8.535627635811297</v>
+        <v>-10.16518542204945</v>
       </c>
       <c r="F6">
-        <v>-0.5087113380829206</v>
+        <v>-1.21274079372222</v>
       </c>
       <c r="G6">
-        <v>-4.253492686435672</v>
+        <v>-4.647719070343164</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.63318292853163</v>
       </c>
       <c r="E7">
-        <v>-9.439320851833978</v>
+        <v>-11.11548116408507</v>
       </c>
       <c r="F7">
-        <v>-0.6080060819216917</v>
+        <v>-1.296619620194893</v>
       </c>
       <c r="G7">
-        <v>-4.123096918734859</v>
+        <v>-4.05177783618234</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.261578021731331</v>
       </c>
       <c r="E8">
-        <v>-11.37441930784366</v>
+        <v>-11.30046027035039</v>
       </c>
       <c r="F8">
-        <v>-0.6153263646602309</v>
+        <v>-1.305219730570757</v>
       </c>
       <c r="G8">
-        <v>-3.604768114196709</v>
+        <v>-3.443564409707437</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.955394600611394</v>
       </c>
       <c r="E9">
-        <v>-11.94063252691872</v>
+        <v>-12.03188127817327</v>
       </c>
       <c r="F9">
-        <v>-0.4621073880014204</v>
+        <v>-1.15417356160949</v>
       </c>
       <c r="G9">
-        <v>-3.105094233772351</v>
+        <v>-3.260921612305846</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.705934123969202</v>
       </c>
       <c r="E10">
-        <v>-12.56125083272192</v>
+        <v>-12.85368157024124</v>
       </c>
       <c r="F10">
-        <v>-0.7605085207770806</v>
+        <v>-1.367765611319134</v>
       </c>
       <c r="G10">
-        <v>-2.318323223091318</v>
+        <v>-2.756463993577241</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.501586222964033</v>
       </c>
       <c r="E11">
-        <v>-12.2396567225932</v>
+        <v>-13.66678266374048</v>
       </c>
       <c r="F11">
-        <v>-0.4099119579510235</v>
+        <v>-1.504683145858253</v>
       </c>
       <c r="G11">
-        <v>-1.782842482114203</v>
+        <v>-2.099476299672257</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.331017854223492</v>
       </c>
       <c r="E12">
-        <v>-13.86319616687517</v>
+        <v>-14.13315208789442</v>
       </c>
       <c r="F12">
-        <v>-0.5677996132920121</v>
+        <v>-1.565106749320657</v>
       </c>
       <c r="G12">
-        <v>-1.218765248768864</v>
+        <v>-1.256459120279006</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.174226702019894</v>
       </c>
       <c r="E13">
-        <v>-14.11149692518974</v>
+        <v>-14.50436468772518</v>
       </c>
       <c r="F13">
-        <v>-0.4953986455525297</v>
+        <v>-1.273622484358373</v>
       </c>
       <c r="G13">
-        <v>-1.07306482904</v>
+        <v>-0.5727553238721027</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.022552905766624</v>
       </c>
       <c r="E14">
-        <v>-15.8177489472218</v>
+        <v>-16.27068691746899</v>
       </c>
       <c r="F14">
-        <v>-0.6993592674698239</v>
+        <v>-1.445908821894822</v>
       </c>
       <c r="G14">
-        <v>-0.8648315146198424</v>
+        <v>-0.1133542299329794</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.859227574545432</v>
       </c>
       <c r="E15">
-        <v>-16.55749329027078</v>
+        <v>-15.736394911674</v>
       </c>
       <c r="F15">
-        <v>-0.3553797034573293</v>
+        <v>-1.265421647070658</v>
       </c>
       <c r="G15">
-        <v>0.6367193834452327</v>
+        <v>0.3562069282661673</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.676768320365625</v>
       </c>
       <c r="E16">
-        <v>-17.29878184295638</v>
+        <v>-18.58016337664079</v>
       </c>
       <c r="F16">
-        <v>-0.208980675625767</v>
+        <v>-1.074440713987829</v>
       </c>
       <c r="G16">
-        <v>0.4922869026579094</v>
+        <v>0.8990172170672281</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.469969989960262</v>
       </c>
       <c r="E17">
-        <v>-17.59575916837941</v>
+        <v>-19.02134089989006</v>
       </c>
       <c r="F17">
-        <v>-0.1861889749051414</v>
+        <v>-1.03810189276182</v>
       </c>
       <c r="G17">
-        <v>1.029644722955791</v>
+        <v>0.6692388722774937</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.240102152503997</v>
       </c>
       <c r="E18">
-        <v>-19.32074095890719</v>
+        <v>-19.1129338151692</v>
       </c>
       <c r="F18">
-        <v>0.4012966424668932</v>
+        <v>-0.7742643898679693</v>
       </c>
       <c r="G18">
-        <v>2.098619877586457</v>
+        <v>1.082494271944716</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.996863549352595</v>
       </c>
       <c r="E19">
-        <v>-19.56366189010065</v>
+        <v>-20.29384662451944</v>
       </c>
       <c r="F19">
-        <v>0.715837685718699</v>
+        <v>-0.3487900407680592</v>
       </c>
       <c r="G19">
-        <v>2.529368199883188</v>
+        <v>2.60880805064354</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.751240957861554</v>
       </c>
       <c r="E20">
-        <v>-20.65685815792231</v>
+        <v>-20.36219488271721</v>
       </c>
       <c r="F20">
-        <v>0.6306707479346735</v>
+        <v>-0.2315694263327067</v>
       </c>
       <c r="G20">
-        <v>2.390308734506102</v>
+        <v>1.898540436829524</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.522254763544319</v>
       </c>
       <c r="E21">
-        <v>-21.58395452761663</v>
+        <v>-21.31571489824629</v>
       </c>
       <c r="F21">
-        <v>1.042759508172746</v>
+        <v>0.07577476092357702</v>
       </c>
       <c r="G21">
-        <v>2.778516546623198</v>
+        <v>1.527686504429287</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.325366861868032</v>
       </c>
       <c r="E22">
-        <v>-22.20104062369386</v>
+        <v>-21.35136757410868</v>
       </c>
       <c r="F22">
-        <v>1.419423136430098</v>
+        <v>0.4252165795901316</v>
       </c>
       <c r="G22">
-        <v>2.610456702322097</v>
+        <v>2.247263372299733</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.177060921389646</v>
       </c>
       <c r="E23">
-        <v>-21.03648919093333</v>
+        <v>-21.91863139915351</v>
       </c>
       <c r="F23">
-        <v>1.568199578707695</v>
+        <v>0.6210600293273936</v>
       </c>
       <c r="G23">
-        <v>2.513633176935032</v>
+        <v>1.704840417326767</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.09124452314935</v>
       </c>
       <c r="E24">
-        <v>-22.50467480590816</v>
+        <v>-22.24356299462588</v>
       </c>
       <c r="F24">
-        <v>1.642815600882263</v>
+        <v>0.8046916868125852</v>
       </c>
       <c r="G24">
-        <v>1.839443888407994</v>
+        <v>1.106975756207626</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.075292901307114</v>
       </c>
       <c r="E25">
-        <v>-22.88877997123875</v>
+        <v>-23.00968569876955</v>
       </c>
       <c r="F25">
-        <v>2.043061192362511</v>
+        <v>0.803894797371092</v>
       </c>
       <c r="G25">
-        <v>2.187898669689522</v>
+        <v>1.060343411741452</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.135579890422999</v>
       </c>
       <c r="E26">
-        <v>-23.03456513496769</v>
+        <v>-22.4843329006657</v>
       </c>
       <c r="F26">
-        <v>2.033843119904159</v>
+        <v>1.223482767706709</v>
       </c>
       <c r="G26">
-        <v>1.641072689149325</v>
+        <v>0.7478510866530272</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.269940757233613</v>
       </c>
       <c r="E27">
-        <v>-22.57581713256866</v>
+        <v>-23.16796945075965</v>
       </c>
       <c r="F27">
-        <v>2.139903968688996</v>
+        <v>1.313196614164701</v>
       </c>
       <c r="G27">
-        <v>1.328010950228146</v>
+        <v>0.6659250161926832</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.473945139025986</v>
       </c>
       <c r="E28">
-        <v>-22.97589422572431</v>
+        <v>-21.48211820413215</v>
       </c>
       <c r="F28">
-        <v>2.26172036547508</v>
+        <v>1.534337576016057</v>
       </c>
       <c r="G28">
-        <v>0.598889779567981</v>
+        <v>0.1756100480078455</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.735668382272799</v>
       </c>
       <c r="E29">
-        <v>-22.86830221177607</v>
+        <v>-22.08624380759942</v>
       </c>
       <c r="F29">
-        <v>2.473446103426217</v>
+        <v>1.517884542661653</v>
       </c>
       <c r="G29">
-        <v>0.605471144100052</v>
+        <v>0.05981709668075717</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.039461921124615</v>
       </c>
       <c r="E30">
-        <v>-22.27023570653106</v>
+        <v>-22.40484459640906</v>
       </c>
       <c r="F30">
-        <v>2.659046790227863</v>
+        <v>1.486131563377542</v>
       </c>
       <c r="G30">
-        <v>-0.4257571702918442</v>
+        <v>-0.5977400110569824</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.368524882128612</v>
       </c>
       <c r="E31">
-        <v>-21.89256097429135</v>
+        <v>-20.95927418062855</v>
       </c>
       <c r="F31">
-        <v>2.609841766501573</v>
+        <v>1.699636634509893</v>
       </c>
       <c r="G31">
-        <v>-0.02514805458463785</v>
+        <v>-0.7645915062362502</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.700741565343622</v>
       </c>
       <c r="E32">
-        <v>-21.23282118153588</v>
+        <v>-20.96394303733046</v>
       </c>
       <c r="F32">
-        <v>2.527505360132913</v>
+        <v>1.30770453828414</v>
       </c>
       <c r="G32">
-        <v>-0.5736822766230987</v>
+        <v>-1.223075579060996</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.01901424618596</v>
       </c>
       <c r="E33">
-        <v>-21.13078107672105</v>
+        <v>-22.08470412643681</v>
       </c>
       <c r="F33">
-        <v>2.508847212752257</v>
+        <v>1.334931318079354</v>
       </c>
       <c r="G33">
-        <v>-0.6763952625245265</v>
+        <v>-1.433695796814968</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.302601292084404</v>
       </c>
       <c r="E34">
-        <v>-20.84567741014614</v>
+        <v>-21.15870364745234</v>
       </c>
       <c r="F34">
-        <v>2.390866157041135</v>
+        <v>1.486951647106314</v>
       </c>
       <c r="G34">
-        <v>-0.2740547315002813</v>
+        <v>-1.812180536683225</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.535795591727649</v>
       </c>
       <c r="E35">
-        <v>-20.65788159304805</v>
+        <v>-20.86510909211305</v>
       </c>
       <c r="F35">
-        <v>2.513217679169427</v>
+        <v>1.747307521806199</v>
       </c>
       <c r="G35">
-        <v>-0.9219351146267312</v>
+        <v>-1.665702138752632</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.704494977941418</v>
       </c>
       <c r="E36">
-        <v>-19.79244492544217</v>
+        <v>-20.35711846335461</v>
       </c>
       <c r="F36">
-        <v>2.368147352651955</v>
+        <v>1.371212153587167</v>
       </c>
       <c r="G36">
-        <v>-1.100270892281731</v>
+        <v>-2.025978878154897</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.800464437545659</v>
       </c>
       <c r="E37">
-        <v>-19.0169346946806</v>
+        <v>-19.73582994339827</v>
       </c>
       <c r="F37">
-        <v>2.235205981646274</v>
+        <v>1.292378084597544</v>
       </c>
       <c r="G37">
-        <v>-1.153163478362667</v>
+        <v>-1.764985399475375</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.821406658325722</v>
       </c>
       <c r="E38">
-        <v>-19.5759114122914</v>
+        <v>-18.90879473537743</v>
       </c>
       <c r="F38">
-        <v>2.01458357778907</v>
+        <v>1.627326787184718</v>
       </c>
       <c r="G38">
-        <v>-1.486664525443307</v>
+        <v>-1.796587867193257</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.769188171781837</v>
       </c>
       <c r="E39">
-        <v>-18.66188421858321</v>
+        <v>-18.36724358574815</v>
       </c>
       <c r="F39">
-        <v>1.955143246433789</v>
+        <v>1.091445973904885</v>
       </c>
       <c r="G39">
-        <v>-0.3459465384310944</v>
+        <v>-1.274081154184547</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.653075009717548</v>
       </c>
       <c r="E40">
-        <v>-16.99661488632057</v>
+        <v>-17.71368516001315</v>
       </c>
       <c r="F40">
-        <v>2.130677612556616</v>
+        <v>1.277068198259003</v>
       </c>
       <c r="G40">
-        <v>-0.8186527148925486</v>
+        <v>-0.8884125304960712</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.483904793009606</v>
       </c>
       <c r="E41">
-        <v>-17.37617799222148</v>
+        <v>-17.44639651018441</v>
       </c>
       <c r="F41">
-        <v>2.182563233198365</v>
+        <v>1.027065259359307</v>
       </c>
       <c r="G41">
-        <v>-0.2954805822304444</v>
+        <v>-1.468234718426184</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.278132965725569</v>
       </c>
       <c r="E42">
-        <v>-16.02339600885812</v>
+        <v>-17.56165975910165</v>
       </c>
       <c r="F42">
-        <v>1.845452491689884</v>
+        <v>0.5769917118658627</v>
       </c>
       <c r="G42">
-        <v>0.09142287494417919</v>
+        <v>-0.3776185276053018</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.050765448616755</v>
       </c>
       <c r="E43">
-        <v>-16.39139792061745</v>
+        <v>-16.42904312504321</v>
       </c>
       <c r="F43">
-        <v>1.659931328158907</v>
+        <v>0.912172357325821</v>
       </c>
       <c r="G43">
-        <v>-0.5301486027816825</v>
+        <v>-0.7729671864506062</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.820048167819829</v>
       </c>
       <c r="E44">
-        <v>-16.38789741020952</v>
+        <v>-16.1564516321515</v>
       </c>
       <c r="F44">
-        <v>1.854542995568206</v>
+        <v>0.7898771641809188</v>
       </c>
       <c r="G44">
-        <v>-0.115608711445223</v>
+        <v>-0.03360649843747573</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.599399520890959</v>
       </c>
       <c r="E45">
-        <v>-13.88427168490686</v>
+        <v>-14.7520450451007</v>
       </c>
       <c r="F45">
-        <v>1.507158841530205</v>
+        <v>0.8663603264813972</v>
       </c>
       <c r="G45">
-        <v>0.1947185168605188</v>
+        <v>-0.3317476086131603</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.402291024954653</v>
       </c>
       <c r="E46">
-        <v>-14.34676926378425</v>
+        <v>-14.99414179402477</v>
       </c>
       <c r="F46">
-        <v>1.317714529979569</v>
+        <v>0.6732057573336224</v>
       </c>
       <c r="G46">
-        <v>-0.1369054508993546</v>
+        <v>-0.0576013325061133</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.23670166501987</v>
       </c>
       <c r="E47">
-        <v>-13.76475619889643</v>
+        <v>-14.48860106970448</v>
       </c>
       <c r="F47">
-        <v>1.487150455282986</v>
+        <v>0.5441469443448623</v>
       </c>
       <c r="G47">
-        <v>0.6324024320620232</v>
+        <v>-0.315141912188176</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.106324539840099</v>
       </c>
       <c r="E48">
-        <v>-12.43317653083699</v>
+        <v>-13.69559734385129</v>
       </c>
       <c r="F48">
-        <v>1.345226268161346</v>
+        <v>0.6397421993627308</v>
       </c>
       <c r="G48">
-        <v>0.04754821491221815</v>
+        <v>-0.4479411359505004</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.013121216364268</v>
       </c>
       <c r="E49">
-        <v>-12.5782960088868</v>
+        <v>-13.84989151024063</v>
       </c>
       <c r="F49">
-        <v>1.501222760721744</v>
+        <v>0.3196891994126971</v>
       </c>
       <c r="G49">
-        <v>0.3385087518132235</v>
+        <v>0.4857783701277023</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.953394088154228</v>
       </c>
       <c r="E50">
-        <v>-12.06847134815525</v>
+        <v>-12.67601594949831</v>
       </c>
       <c r="F50">
-        <v>1.448613146969947</v>
+        <v>0.4859425371545578</v>
       </c>
       <c r="G50">
-        <v>0.2772603487911673</v>
+        <v>0.06870922199923957</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.925346769513375</v>
       </c>
       <c r="E51">
-        <v>-11.28815640647155</v>
+        <v>-12.03081255830746</v>
       </c>
       <c r="F51">
-        <v>1.339674549827784</v>
+        <v>0.3151828807414677</v>
       </c>
       <c r="G51">
-        <v>0.7498705194319827</v>
+        <v>-0.6043081334068964</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.922082855217229</v>
       </c>
       <c r="E52">
-        <v>-10.36006830096955</v>
+        <v>-11.83288201638021</v>
       </c>
       <c r="F52">
-        <v>1.187349381596594</v>
+        <v>-0.02563231979233285</v>
       </c>
       <c r="G52">
-        <v>-0.1706233572168316</v>
+        <v>-1.045961392709987</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.940900207001754</v>
       </c>
       <c r="E53">
-        <v>-10.74985670117977</v>
+        <v>-11.5599418309899</v>
       </c>
       <c r="F53">
-        <v>1.039533845506245</v>
+        <v>0.3014667732859135</v>
       </c>
       <c r="G53">
-        <v>-0.2281771914170612</v>
+        <v>-0.5868781111426336</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.9775842842398</v>
       </c>
       <c r="E54">
-        <v>-8.976655719418314</v>
+        <v>-10.77947292118994</v>
       </c>
       <c r="F54">
-        <v>0.7889411090157554</v>
+        <v>0.295680626977359</v>
       </c>
       <c r="G54">
-        <v>-0.6641528651203017</v>
+        <v>-0.8619712032739122</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.028027788487651</v>
       </c>
       <c r="E55">
-        <v>-9.888708498459154</v>
+        <v>-10.02336267307723</v>
       </c>
       <c r="F55">
-        <v>0.9792800573614145</v>
+        <v>0.2950792322429265</v>
       </c>
       <c r="G55">
-        <v>-0.5717654707558606</v>
+        <v>-1.400951190886036</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.092962845334259</v>
       </c>
       <c r="E56">
-        <v>-8.47058063516512</v>
+        <v>-10.06406912593218</v>
       </c>
       <c r="F56">
-        <v>0.9570963783144438</v>
+        <v>0.151519847868161</v>
       </c>
       <c r="G56">
-        <v>-1.075481527283668</v>
+        <v>-1.095420943066698</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.17042949699862</v>
       </c>
       <c r="E57">
-        <v>-8.251796470432543</v>
+        <v>-9.998161715224548</v>
       </c>
       <c r="F57">
-        <v>0.8383780756148299</v>
+        <v>0.1101520081397565</v>
       </c>
       <c r="G57">
-        <v>-1.589470206619834</v>
+        <v>-1.767130632984822</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.261930046248971</v>
       </c>
       <c r="E58">
-        <v>-7.762381642053569</v>
+        <v>-10.00127277686782</v>
       </c>
       <c r="F58">
-        <v>1.21003173782005</v>
+        <v>-0.03989100789672075</v>
       </c>
       <c r="G58">
-        <v>-1.219208861871127</v>
+        <v>-2.29473889666955</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.365721617315731</v>
       </c>
       <c r="E59">
-        <v>-8.197993670747412</v>
+        <v>-9.151359718160229</v>
       </c>
       <c r="F59">
-        <v>0.6481766362580355</v>
+        <v>-0.01057757061385464</v>
       </c>
       <c r="G59">
-        <v>-2.084886725480689</v>
+        <v>-2.121405353324389</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.481362371909916</v>
       </c>
       <c r="E60">
-        <v>-7.847394684599564</v>
+        <v>-9.207539966699388</v>
       </c>
       <c r="F60">
-        <v>0.7216611085603796</v>
+        <v>-0.1503372337119788</v>
       </c>
       <c r="G60">
-        <v>-1.656574964700861</v>
+        <v>-2.526510189873926</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.607323649061782</v>
       </c>
       <c r="E61">
-        <v>-7.392024923810256</v>
+        <v>-9.703792790829944</v>
       </c>
       <c r="F61">
-        <v>0.7233890829626193</v>
+        <v>0.1914703509703756</v>
       </c>
       <c r="G61">
-        <v>-2.748528615919609</v>
+        <v>-3.276361996701007</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.73934517523622</v>
       </c>
       <c r="E62">
-        <v>-6.726117349456338</v>
+        <v>-8.540993877510386</v>
       </c>
       <c r="F62">
-        <v>0.7200076872243917</v>
+        <v>-0.04242995398630123</v>
       </c>
       <c r="G62">
-        <v>-2.546883287122601</v>
+        <v>-3.175065924290387</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.876307780312259</v>
       </c>
       <c r="E63">
-        <v>-6.835443768949515</v>
+        <v>-7.940160474646691</v>
       </c>
       <c r="F63">
-        <v>0.5423270211609118</v>
+        <v>-0.1975574891411618</v>
       </c>
       <c r="G63">
-        <v>-2.719508373722357</v>
+        <v>-2.578919436306128</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.011842489856051</v>
       </c>
       <c r="E64">
-        <v>-5.875058586824809</v>
+        <v>-8.218091038393451</v>
       </c>
       <c r="F64">
-        <v>0.4599765325464045</v>
+        <v>0.1187885666813441</v>
       </c>
       <c r="G64">
-        <v>-3.114314103099221</v>
+        <v>-3.514039303147442</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.144094097489595</v>
       </c>
       <c r="E65">
-        <v>-5.865770686635077</v>
+        <v>-7.628610519866986</v>
       </c>
       <c r="F65">
-        <v>0.502092388039537</v>
+        <v>-0.09296036555707107</v>
       </c>
       <c r="G65">
-        <v>-3.410055067758934</v>
+        <v>-3.077931207622631</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.268102091390521</v>
       </c>
       <c r="E66">
-        <v>-6.655174275652174</v>
+        <v>-7.522920465001968</v>
       </c>
       <c r="F66">
-        <v>0.6293776664189035</v>
+        <v>0.04935563934609239</v>
       </c>
       <c r="G66">
-        <v>-3.674137285426597</v>
+        <v>-3.53780570957387</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.382865845625918</v>
       </c>
       <c r="E67">
-        <v>-6.334657942337281</v>
+        <v>-7.743461677649522</v>
       </c>
       <c r="F67">
-        <v>0.3289205257494948</v>
+        <v>-0.03129338262306468</v>
       </c>
       <c r="G67">
-        <v>-3.727715154434162</v>
+        <v>-3.488061452300781</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.488595540546911</v>
       </c>
       <c r="E68">
-        <v>-5.8468914784971</v>
+        <v>-7.860060826399018</v>
       </c>
       <c r="F68">
-        <v>0.2867425427011523</v>
+        <v>0.03936967030534435</v>
       </c>
       <c r="G68">
-        <v>-3.729777624305128</v>
+        <v>-3.736001449918958</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.586869237926332</v>
       </c>
       <c r="E69">
-        <v>-6.72216852012165</v>
+        <v>-8.006217324996578</v>
       </c>
       <c r="F69">
-        <v>-0.07778633147258973</v>
+        <v>-0.411802292364212</v>
       </c>
       <c r="G69">
-        <v>-4.014759315962209</v>
+        <v>-4.210836307162163</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.683389454919926</v>
       </c>
       <c r="E70">
-        <v>-6.446456908638647</v>
+        <v>-8.099155197055998</v>
       </c>
       <c r="F70">
-        <v>-0.2124821846374005</v>
+        <v>-0.7206010927798117</v>
       </c>
       <c r="G70">
-        <v>-3.96828918822746</v>
+        <v>-4.728221606221622</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.779161002504631</v>
       </c>
       <c r="E71">
-        <v>-6.184004669050104</v>
+        <v>-7.91985026872229</v>
       </c>
       <c r="F71">
-        <v>-0.007662545723403179</v>
+        <v>-0.5593328700679984</v>
       </c>
       <c r="G71">
-        <v>-3.659938355608663</v>
+        <v>-4.329499501471799</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.880737991863666</v>
       </c>
       <c r="E72">
-        <v>-5.662727497553162</v>
+        <v>-7.334757841509257</v>
       </c>
       <c r="F72">
-        <v>-0.06862790146723839</v>
+        <v>-0.7204975468544618</v>
       </c>
       <c r="G72">
-        <v>-4.54984941256569</v>
+        <v>-4.02456846239507</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.987795606926838</v>
       </c>
       <c r="E73">
-        <v>-5.933525714737841</v>
+        <v>-8.036028269389073</v>
       </c>
       <c r="F73">
-        <v>-0.1312450218122558</v>
+        <v>-0.340614054502428</v>
       </c>
       <c r="G73">
-        <v>-4.237307429294176</v>
+        <v>-3.829855415957296</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.102084808079335</v>
       </c>
       <c r="E74">
-        <v>-6.53419609253726</v>
+        <v>-8.528300564866887</v>
       </c>
       <c r="F74">
-        <v>-0.1786972201142227</v>
+        <v>-0.8110936045964353</v>
       </c>
       <c r="G74">
-        <v>-3.951600728163994</v>
+        <v>-4.182057734789279</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.219818289025006</v>
       </c>
       <c r="E75">
-        <v>-7.489459570559291</v>
+        <v>-7.857493181636669</v>
       </c>
       <c r="F75">
-        <v>-0.08738048273181361</v>
+        <v>-0.5082076907020184</v>
       </c>
       <c r="G75">
-        <v>-3.430812188290165</v>
+        <v>-3.851556041967219</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.337854895497771</v>
       </c>
       <c r="E76">
-        <v>-7.294744245177482</v>
+        <v>-8.974169587188102</v>
       </c>
       <c r="F76">
-        <v>-0.3087567009255647</v>
+        <v>-0.5776696108963681</v>
       </c>
       <c r="G76">
-        <v>-3.163224102896414</v>
+        <v>-4.073144097092796</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.451117136587674</v>
       </c>
       <c r="E77">
-        <v>-7.207530364263758</v>
+        <v>-9.263208497675679</v>
       </c>
       <c r="F77">
-        <v>-0.2267069096782736</v>
+        <v>-0.8648032902591496</v>
       </c>
       <c r="G77">
-        <v>-2.927513260500305</v>
+        <v>-4.110953837696812</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.551196535113118</v>
       </c>
       <c r="E78">
-        <v>-7.883391524486536</v>
+        <v>-9.118233930794119</v>
       </c>
       <c r="F78">
-        <v>-0.2676423416224168</v>
+        <v>-0.7984676286429652</v>
       </c>
       <c r="G78">
-        <v>-2.668717984058859</v>
+        <v>-3.855131431149631</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.633001603264652</v>
       </c>
       <c r="E79">
-        <v>-8.592582253405768</v>
+        <v>-9.767408793689697</v>
       </c>
       <c r="F79">
-        <v>-0.09126635421834609</v>
+        <v>-0.9785323360917021</v>
       </c>
       <c r="G79">
-        <v>-2.904528142821146</v>
+        <v>-3.830451314154364</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.687160474235898</v>
       </c>
       <c r="E80">
-        <v>-8.097715142321558</v>
+        <v>-11.22661444470731</v>
       </c>
       <c r="F80">
-        <v>-0.4333646958590831</v>
+        <v>-1.118483352059873</v>
       </c>
       <c r="G80">
-        <v>-3.205314378882708</v>
+        <v>-3.721200000812876</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.709943325982188</v>
       </c>
       <c r="E81">
-        <v>-10.52468738809638</v>
+        <v>-10.93809630873061</v>
       </c>
       <c r="F81">
-        <v>-0.4897251572107559</v>
+        <v>-1.154052619968681</v>
       </c>
       <c r="G81">
-        <v>-2.64431926343443</v>
+        <v>-3.212703516526361</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.696359626605592</v>
       </c>
       <c r="E82">
-        <v>-10.88537128585931</v>
+        <v>-11.29772960052376</v>
       </c>
       <c r="F82">
-        <v>-0.5543485834053538</v>
+        <v>-0.7668620987565529</v>
       </c>
       <c r="G82">
-        <v>-2.089822748879742</v>
+        <v>-3.380101251719609</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.648560721717301</v>
       </c>
       <c r="E83">
-        <v>-11.3916229805988</v>
+        <v>-12.48312107066759</v>
       </c>
       <c r="F83">
-        <v>-0.6413230188622878</v>
+        <v>-1.122178699043762</v>
       </c>
       <c r="G83">
-        <v>-2.359095901952982</v>
+        <v>-3.211375987765113</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.56787137404841</v>
       </c>
       <c r="E84">
-        <v>-12.73768018006076</v>
+        <v>-13.76442109181986</v>
       </c>
       <c r="F84">
-        <v>-0.7003541367205862</v>
+        <v>-1.530756009861367</v>
       </c>
       <c r="G84">
-        <v>-1.357976999240757</v>
+        <v>-2.778780381057469</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.459536380128597</v>
       </c>
       <c r="E85">
-        <v>-13.44013706813059</v>
+        <v>-15.05132283531962</v>
       </c>
       <c r="F85">
-        <v>-1.092024468847054</v>
+        <v>-1.295956926272653</v>
       </c>
       <c r="G85">
-        <v>-1.611525061002459</v>
+        <v>-3.145274324982485</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.329185841481161</v>
       </c>
       <c r="E86">
-        <v>-15.12632342183466</v>
+        <v>-16.78606801580795</v>
       </c>
       <c r="F86">
-        <v>-0.8281447192156604</v>
+        <v>-1.316709186447586</v>
       </c>
       <c r="G86">
-        <v>-1.507474614703165</v>
+        <v>-2.165842806098026</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.181187431221374</v>
       </c>
       <c r="E87">
-        <v>-15.78074678610512</v>
+        <v>-16.25245528111411</v>
       </c>
       <c r="F87">
-        <v>-1.074143330090224</v>
+        <v>-1.313708011347244</v>
       </c>
       <c r="G87">
-        <v>-0.6004612794902633</v>
+        <v>-3.164389414926237</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.023332096590557</v>
       </c>
       <c r="E88">
-        <v>-16.53878163567109</v>
+        <v>-18.59467713583538</v>
       </c>
       <c r="F88">
-        <v>-0.914757158117571</v>
+        <v>-1.342983343729581</v>
       </c>
       <c r="G88">
-        <v>-0.7861994369710732</v>
+        <v>-2.1832231701792</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.859832149889228</v>
       </c>
       <c r="E89">
-        <v>-19.11570976973591</v>
+        <v>-20.35655693257766</v>
       </c>
       <c r="F89">
-        <v>-0.987845670801377</v>
+        <v>-1.342853290047342</v>
       </c>
       <c r="G89">
-        <v>-0.8679798434276894</v>
+        <v>-1.800001039644246</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.699181200308498</v>
       </c>
       <c r="E90">
-        <v>-20.1221359470966</v>
+        <v>-22.0101337449525</v>
       </c>
       <c r="F90">
-        <v>-1.017458148716654</v>
+        <v>-1.546231569680468</v>
       </c>
       <c r="G90">
-        <v>-0.3211306890687176</v>
+        <v>-2.108775622092069</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.544107314641978</v>
       </c>
       <c r="E91">
-        <v>-22.43593257047172</v>
+        <v>-23.22588410484375</v>
       </c>
       <c r="F91">
-        <v>-1.210703009911334</v>
+        <v>-1.52249221665104</v>
       </c>
       <c r="G91">
-        <v>-0.9995177493395514</v>
+        <v>-2.681288125471471</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.402269420947314</v>
       </c>
       <c r="E92">
-        <v>-23.49810426286683</v>
+        <v>-24.41231712400933</v>
       </c>
       <c r="F92">
-        <v>-1.607273963592763</v>
+        <v>-1.904636323645313</v>
       </c>
       <c r="G92">
-        <v>-0.3515843974844732</v>
+        <v>-2.259269711761799</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.278012939382172</v>
       </c>
       <c r="E93">
-        <v>-25.55711988162241</v>
+        <v>-26.89869842029078</v>
       </c>
       <c r="F93">
-        <v>-1.248448398987296</v>
+        <v>-1.935348873471507</v>
       </c>
       <c r="G93">
-        <v>-1.061146865098624</v>
+        <v>-2.882509704439453</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.175258951830866</v>
       </c>
       <c r="E94">
-        <v>-28.0256363479436</v>
+        <v>-28.69319681531031</v>
       </c>
       <c r="F94">
-        <v>-1.392598409320257</v>
+        <v>-1.82631418571062</v>
       </c>
       <c r="G94">
-        <v>-0.9115664859977338</v>
+        <v>-2.607174942483808</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.099554199303237</v>
       </c>
       <c r="E95">
-        <v>-30.70346793984733</v>
+        <v>-31.62983975370042</v>
       </c>
       <c r="F95">
-        <v>-1.795520455878951</v>
+        <v>-2.033908027056593</v>
       </c>
       <c r="G95">
-        <v>-1.624436188605616</v>
+        <v>-2.804552978080695</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.054352562494667</v>
       </c>
       <c r="E96">
-        <v>-32.66946870248535</v>
+        <v>-33.69274306739158</v>
       </c>
       <c r="F96">
-        <v>-1.778089948989244</v>
+        <v>-2.08425122759433</v>
       </c>
       <c r="G96">
-        <v>-1.544277949463243</v>
+        <v>-3.513128903124143</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.041290632318011</v>
       </c>
       <c r="E97">
-        <v>-35.28230537119398</v>
+        <v>-35.70403989129132</v>
       </c>
       <c r="F97">
-        <v>-1.904101198303105</v>
+        <v>-2.535524251087028</v>
       </c>
       <c r="G97">
-        <v>-1.784345469789032</v>
+        <v>-2.877881561775552</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.065845604836779</v>
       </c>
       <c r="E98">
-        <v>-37.16340630313621</v>
+        <v>-38.43840268846981</v>
       </c>
       <c r="F98">
-        <v>-2.284381478641079</v>
+        <v>-2.498928635966151</v>
       </c>
       <c r="G98">
-        <v>-1.984593748368468</v>
+        <v>-3.366574362646146</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.123043983083418</v>
       </c>
       <c r="E99">
-        <v>-40.58311967782054</v>
+        <v>-40.91214274955884</v>
       </c>
       <c r="F99">
-        <v>-2.349379326901742</v>
+        <v>-2.532736794776608</v>
       </c>
       <c r="G99">
-        <v>-2.315611886294655</v>
+        <v>-3.706703121896408</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.227141053459514</v>
       </c>
       <c r="E100">
-        <v>-41.9708592162861</v>
+        <v>-43.60192951284282</v>
       </c>
       <c r="F100">
-        <v>-2.410072978137459</v>
+        <v>-2.970839604932196</v>
       </c>
       <c r="G100">
-        <v>-2.630408351078413</v>
+        <v>-3.804135787662698</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.356272066603835</v>
       </c>
       <c r="E101">
-        <v>-44.97030756068858</v>
+        <v>-45.82800959468937</v>
       </c>
       <c r="F101">
-        <v>-2.72406812727082</v>
+        <v>-2.960206680949861</v>
       </c>
       <c r="G101">
-        <v>-3.098840613248668</v>
+        <v>-4.232411132441594</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.550702832284633</v>
       </c>
       <c r="E102">
-        <v>-47.38969687673756</v>
+        <v>-47.9894932590535</v>
       </c>
       <c r="F102">
-        <v>-2.59448247261388</v>
+        <v>-3.248195235472332</v>
       </c>
       <c r="G102">
-        <v>-3.152603872806432</v>
+        <v>-4.024512183120902</v>
       </c>
     </row>
   </sheetData>
